--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.78557923989119</v>
+        <v>4.677656626482318</v>
       </c>
       <c r="D2" t="n">
-        <v>29.18582723993499</v>
+        <v>4.742696926489436</v>
       </c>
       <c r="E2" t="n">
-        <v>15.35443563672156</v>
+        <v>2.495095790967254</v>
       </c>
       <c r="F2" t="n">
-        <v>15.73654692711007</v>
+        <v>2.557188875655386</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.93119842826756</v>
+        <v>3.076319744593479</v>
       </c>
       <c r="D3" t="n">
-        <v>19.69895156562508</v>
+        <v>3.201079629414076</v>
       </c>
       <c r="E3" t="n">
-        <v>15.35443563672156</v>
+        <v>2.495095790967254</v>
       </c>
       <c r="F3" t="n">
-        <v>15.73654692711007</v>
+        <v>2.557188875655386</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.81659722086769</v>
+        <v>4.520197048391</v>
       </c>
       <c r="D4" t="n">
-        <v>28.639055519346</v>
+        <v>4.653846521893725</v>
       </c>
       <c r="E4" t="n">
-        <v>15.35443563672156</v>
+        <v>2.495095790967254</v>
       </c>
       <c r="F4" t="n">
-        <v>15.73654692711007</v>
+        <v>2.557188875655386</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.90444995940098</v>
+        <v>9.57197311840266</v>
       </c>
       <c r="D5" t="n">
-        <v>10.15415468321727</v>
+        <v>1.650050136022807</v>
       </c>
       <c r="E5" t="n">
-        <v>15.35443563672156</v>
+        <v>2.495095790967254</v>
       </c>
       <c r="F5" t="n">
-        <v>15.73654692711007</v>
+        <v>2.557188875655386</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.84539835318675</v>
+        <v>5.337377232392847</v>
       </c>
       <c r="D6" t="n">
-        <v>28.6574597618142</v>
+        <v>4.656837211294808</v>
       </c>
       <c r="E6" t="n">
-        <v>15.35443563672156</v>
+        <v>2.495095790967254</v>
       </c>
       <c r="F6" t="n">
-        <v>15.73654692711007</v>
+        <v>2.557188875655386</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.9275515025401</v>
+        <v>2.100727119162766</v>
       </c>
       <c r="D7" t="n">
-        <v>12.58414585990324</v>
+        <v>2.044923702234276</v>
       </c>
       <c r="E7" t="n">
-        <v>15.35443563672156</v>
+        <v>2.495095790967254</v>
       </c>
       <c r="F7" t="n">
-        <v>15.73654692711007</v>
+        <v>2.557188875655386</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.782751533812169</v>
+        <v>0.9396971242444775</v>
       </c>
       <c r="D8" t="n">
-        <v>5.297062881585203</v>
+        <v>0.8607727182575955</v>
       </c>
       <c r="E8" t="n">
-        <v>15.35443563672156</v>
+        <v>2.495095790967254</v>
       </c>
       <c r="F8" t="n">
-        <v>15.73654692711007</v>
+        <v>2.557188875655386</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.86253002844496</v>
+        <v>2.740161129622306</v>
       </c>
       <c r="D9" t="n">
-        <v>16.41601874987116</v>
+        <v>2.667603046854064</v>
       </c>
       <c r="E9" t="n">
-        <v>15.35443563672156</v>
+        <v>2.495095790967254</v>
       </c>
       <c r="F9" t="n">
-        <v>15.73654692711007</v>
+        <v>2.557188875655386</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>1.880537929023062</v>
+        <v>0.3055874134662476</v>
       </c>
       <c r="D10" t="n">
-        <v>10.5</v>
+        <v>1.70625</v>
       </c>
       <c r="E10" t="n">
-        <v>15.35443563672156</v>
+        <v>2.495095790967254</v>
       </c>
       <c r="F10" t="n">
-        <v>15.73654692711007</v>
+        <v>2.557188875655386</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.36685641343161</v>
+        <v>2.984614167182636</v>
       </c>
       <c r="D11" t="n">
-        <v>62.75746967493193</v>
+        <v>10.19808882217644</v>
       </c>
       <c r="E11" t="n">
-        <v>15.35443563672156</v>
+        <v>2.495095790967254</v>
       </c>
       <c r="F11" t="n">
-        <v>15.73654692711007</v>
+        <v>2.557188875655386</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
